--- a/tf_idf_lemma_and_words/feature_importance.xlsx
+++ b/tf_idf_lemma_and_words/feature_importance.xlsx
@@ -451,47 +451,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.271908730923303</v>
+        <v>1.259859361364255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>government</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.270538670049346</v>
+        <v>1.153554450913934</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>government</t>
+          <t>bill</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.1633763266126</v>
+        <v>1.116218451391909</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>people</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.110790091561748</v>
+        <v>1.099004257033443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>long</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.110555457975571</v>
+        <v>1.090117236266193</v>
       </c>
     </row>
     <row r="7">
@@ -501,947 +501,947 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.082338551549029</v>
+        <v>1.05978056973143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>david</t>
+          <t>would</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.048926941697125</v>
+        <v>1.037879028038247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>also</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.045690631489637</v>
+        <v>1.034867280056703</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>david</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.042797507970882</v>
+        <v>1.031386951378943</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>work</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.031066120791439</v>
+        <v>1.031186293276131</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>house</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.019443659140185</v>
+        <v>1.031093831323382</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>years</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.016665193480099</v>
+        <v>1.023640481675483</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>right</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.014010882822764</v>
+        <v>1.005151912060954</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mark</t>
+          <t>john</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.004901271423187</v>
+        <v>0.9965962805535657</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>green</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.004723637002617</v>
+        <v>0.9943039181370354</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9982165493963635</v>
+        <v>0.9935552925675648</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>member</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9915958633956654</v>
+        <v>0.9879021696944947</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>many</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9863155237185273</v>
+        <v>0.9839776960698352</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>members</t>
+          <t>mark</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9673931620648615</v>
+        <v>0.9836503230737172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>support</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9668959069108338</v>
+        <v>0.9793033961245532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>make</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9562043735280454</v>
+        <v>0.9749426328215528</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>one</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9552639175941149</v>
+        <v>0.9739149741633106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>chris</t>
+          <t>members</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9529024020337988</v>
+        <v>0.9534724483300641</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>west</t>
+          <t>law</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9475557984034382</v>
+        <v>0.9478113779349275</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>know</t>
+          <t>make</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9451791101494873</v>
+        <v>0.9436540323101845</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>first</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9415411014817266</v>
+        <v>0.938010851182412</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>james</t>
+          <t>chris</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9401431584041906</v>
+        <v>0.933794320568336</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>know</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9316544091774545</v>
+        <v>0.9316965449611165</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>west</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9300983774328477</v>
+        <v>0.9302132427329892</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>minister</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9234503165933452</v>
+        <v>0.9275899187191783</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>us</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9214963141253967</v>
+        <v>0.9256965596573952</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>need</t>
+          <t>new</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9133560569801971</v>
+        <v>0.9208018834490765</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>want</t>
+          <t>james</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9003367456420889</v>
+        <v>0.9196995327239614</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8989262517712158</v>
+        <v>0.917483607277403</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>important</t>
+          <t>last</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8917305137710811</v>
+        <v>0.9125278537029361</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>champion</t>
+          <t>minister</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8826109223721454</v>
+        <v>0.9092295301711009</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>paul</t>
+          <t>country</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8825508753083395</v>
+        <v>0.9072922921234492</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>across</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.877230999252296</v>
+        <v>0.9028211425429</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>richard</t>
+          <t>need</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.873819103783089</v>
+        <v>0.8997803405475622</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>andrew</t>
+          <t>place</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.873370300491888</v>
+        <v>0.8877200573359569</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>want</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8720464625057252</v>
+        <v>0.8860515162770164</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hall</t>
+          <t>important</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8698739197628813</v>
+        <v>0.8758412391034387</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>including</t>
+          <t>two</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8678665320971676</v>
+        <v>0.8701069374827135</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>smith</t>
+          <t>day</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8608744152958452</v>
+        <v>0.8674121784492419</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sarah</t>
+          <t>well</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8599734499682</v>
+        <v>0.8673418881183383</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>made</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8555505335384935</v>
+        <v>0.8655751516534651</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>champion</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8531232454705814</v>
+        <v>0.8653782054178722</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>constituency</t>
+          <t>paul</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8516526046534872</v>
+        <v>0.8651879856030227</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>peter</t>
+          <t>get</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8514789838185992</v>
+        <v>0.8632781538828477</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jim</t>
+          <t>local</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8490627868486742</v>
+        <v>0.8608484334164668</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>way</t>
+          <t>andrew</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8461315129012059</v>
+        <v>0.8584236368368934</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ensure</t>
+          <t>take</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8459455522697458</v>
+        <v>0.8572698425704124</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>much</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8452101399299276</v>
+        <v>0.8554616095236595</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>thank</t>
+          <t>including</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8439864500520546</v>
+        <v>0.8547977140233585</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>hall</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8434752954332636</v>
+        <v>0.8517028171712369</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>dr</t>
+          <t>richard</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8432962763410787</v>
+        <v>0.849335464722984</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>stephen</t>
+          <t>smith</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8409396439523118</v>
+        <v>0.8449435301181585</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>like</t>
+          <t>part</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.840902384494723</v>
+        <v>0.8439674791858507</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jones</t>
+          <t>working</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8369357608921904</v>
+        <v>0.8436714010858499</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>debate</t>
+          <t>sarah</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8368743800332926</v>
+        <v>0.843368970150526</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>say</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8322487178744236</v>
+        <v>0.84262407759814</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>george</t>
+          <t>constituency</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8287364534719848</v>
+        <v>0.8419586121426631</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8286785094424254</v>
+        <v>0.8376216570980339</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>labour</t>
+          <t>peter</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8277246694228362</v>
+        <v>0.8348184012596622</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>martin</t>
+          <t>way</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8264536056709642</v>
+        <v>0.8343089670488538</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>secretary</t>
+          <t>may</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.825297896661062</v>
+        <v>0.8339446053438119</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8233334769303751</v>
+        <v>0.8325867236771103</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>hope</t>
+          <t>thank</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8209667552569134</v>
+        <v>0.8316132686946563</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>johnson</t>
+          <t>like</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8205727560006703</v>
+        <v>0.8300575304747454</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>said</t>
+          <t>ensure</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8198703378380012</v>
+        <v>0.829262200115953</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>public</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8143964225645124</v>
+        <v>0.827702731619514</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>national</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8141473961259728</v>
+        <v>0.8274181475540465</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>western</t>
+          <t>debate</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.813116853206769</v>
+        <v>0.8256056764096025</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>stephen</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8093158459757616</v>
+        <v>0.8238252587330357</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>pay</t>
+          <t>jones</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8083337353252293</v>
+        <v>0.8229651702700327</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ben</t>
+          <t>every</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8078554280266065</v>
+        <v>0.8185072545932961</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>great</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.806379158335487</v>
+        <v>0.8171987180467801</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>come</t>
+          <t>labour</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.805180241147784</v>
+        <v>0.8147657500893239</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>000</t>
+          <t>back</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8033082351794767</v>
+        <v>0.8143979940149957</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>tom</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8025827452324198</v>
+        <v>0.8140500748734156</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>steve</t>
+          <t>secretary</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.800211182353521</v>
+        <v>0.8128685075814995</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>does</t>
+          <t>see</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7991214406483378</v>
+        <v>0.8126520636826962</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>world</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7986943313895993</v>
+        <v>0.8110054687373482</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>change</t>
+          <t>could</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7968861324019588</v>
+        <v>0.8109124564006385</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>said</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7942134884158407</v>
+        <v>0.8102464242438444</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>did</t>
+          <t>george</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7919260110525113</v>
+        <v>0.8095449342851833</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>hope</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7898898900360216</v>
+        <v>0.808340126400331</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>johnson</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.789788191507542</v>
+        <v>0.8049642607222867</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>michael</t>
+          <t>martin</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7893817420019755</v>
+        <v>0.8043266045440696</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>making</t>
+          <t>future</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7893440730310526</v>
+        <v>0.8024379588326136</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>parliament</t>
+          <t>national</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7892505981488459</v>
+        <v>0.8020388286637861</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>help</t>
+          <t>go</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7867894549365563</v>
+        <v>0.8011738848915336</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>look</t>
+          <t>ben</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7861759306632286</v>
+        <v>0.7984293735506167</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>sure</t>
+          <t>western</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7850961032663364</v>
+        <v>0.7977859742990314</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>andy</t>
+          <t>since</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7831889809774291</v>
+        <v>0.7958408959291168</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>good</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7769393168902454</v>
+        <v>0.794427512630041</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>forward</t>
+          <t>come</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7765045891363893</v>
+        <v>0.7938933988434214</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>point</t>
+          <t>pay</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7727581332463207</v>
+        <v>0.7937485653536822</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>think</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7703302412733963</v>
+        <v>0.7911238613714472</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>children</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.768782329546265</v>
+        <v>0.7902573945739184</v>
       </c>
     </row>
   </sheetData>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>488.3025639112537</v>
+        <v>516.7816998204174</v>
       </c>
       <c r="C2" t="n">
-        <v>1.835915031527189e-99</v>
+        <v>1.463878683866282e-105</v>
       </c>
     </row>
     <row r="3">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>405.1017381110131</v>
+        <v>410.5737694409939</v>
       </c>
       <c r="C3" t="n">
-        <v>1.116946718610806e-81</v>
+        <v>7.587348478198094e-83</v>
       </c>
     </row>
     <row r="4">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>342.5086467831838</v>
+        <v>349.8372942111918</v>
       </c>
       <c r="C4" t="n">
-        <v>2.43336893061822e-68</v>
+        <v>6.711287387567908e-70</v>
       </c>
     </row>
     <row r="5">
@@ -1521,283 +1521,283 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>326.0413616171584</v>
+        <v>331.6181572337026</v>
       </c>
       <c r="C5" t="n">
-        <v>7.719511598006348e-65</v>
+        <v>5.037620373387381e-66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lock</t>
+          <t>arm</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>248.6505570672518</v>
+        <v>256.3258101633371</v>
       </c>
       <c r="C6" t="n">
-        <v>1.922341838835906e-48</v>
+        <v>4.602675549765036e-50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>arm</t>
+          <t>lock</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>244.7157119738386</v>
+        <v>254.9364602320985</v>
       </c>
       <c r="C7" t="n">
-        <v>1.300839688155189e-47</v>
+        <v>9.047068802674618e-50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>smallest</t>
+          <t>livestock</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>179.7524959631688</v>
+        <v>248.9910353416405</v>
       </c>
       <c r="C8" t="n">
-        <v>5.706976817822154e-34</v>
+        <v>1.629145015917757e-48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>livestock</t>
+          <t>updating</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>179.5180182147597</v>
+        <v>239.6894902206264</v>
       </c>
       <c r="C9" t="n">
-        <v>6.387937537776758e-34</v>
+        <v>1.494075783041822e-46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>updating</t>
+          <t>cancellations</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>163.4542369626809</v>
+        <v>201.4064095629928</v>
       </c>
       <c r="C10" t="n">
-        <v>1.421568291358152e-30</v>
+        <v>1.680220597035419e-38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cancellations</t>
+          <t>passenger</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>155.0661871025029</v>
+        <v>187.5818984764484</v>
       </c>
       <c r="C11" t="n">
-        <v>7.855203418128072e-29</v>
+        <v>1.319355237197214e-35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>federation</t>
+          <t>smallest</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150.6082268499894</v>
+        <v>178.9963784906266</v>
       </c>
       <c r="C12" t="n">
-        <v>6.598468820826773e-28</v>
+        <v>8.208430860566692e-34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>passenger</t>
+          <t>federation</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>130.6354629059695</v>
+        <v>149.896157984172</v>
       </c>
       <c r="C13" t="n">
-        <v>8.777434354654956e-24</v>
+        <v>9.267466687291924e-28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>length</t>
+          <t>dogs</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98.707970130221</v>
+        <v>131.3329517033546</v>
       </c>
       <c r="C14" t="n">
-        <v>2.871273608148167e-17</v>
+        <v>6.307796041412646e-24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lots</t>
+          <t>exploitation</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96.50181238320647</v>
+        <v>121.5355863549701</v>
       </c>
       <c r="C15" t="n">
-        <v>8.007591158507865e-17</v>
+        <v>6.477562948986872e-22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mayor</t>
+          <t>railway</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>93.29357115124809</v>
+        <v>108.9405766820825</v>
       </c>
       <c r="C16" t="n">
-        <v>3.547199951400796e-16</v>
+        <v>2.415738222239074e-19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dogs</t>
+          <t>lots</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>92.54161075256017</v>
+        <v>108.4646084432445</v>
       </c>
       <c r="C17" t="n">
-        <v>5.025085386978333e-16</v>
+        <v>3.019083443532395e-19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exploitation</t>
+          <t>length</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.89950001251879</v>
+        <v>104.3040569075242</v>
       </c>
       <c r="C18" t="n">
-        <v>2.706288706610376e-15</v>
+        <v>2.113595200067804e-18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>craig</t>
+          <t>arap</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.10301363244342</v>
+        <v>90.50387630273305</v>
       </c>
       <c r="C19" t="n">
-        <v>3.908122523743734e-15</v>
+        <v>1.289882527050928e-15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fletcher</t>
+          <t>craig</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>88.04889772882643</v>
+        <v>90.21276300074751</v>
       </c>
       <c r="C20" t="n">
-        <v>4.006888392510038e-15</v>
+        <v>1.475636066583192e-15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>arap</t>
+          <t>fletcher</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>87.86510287434052</v>
+        <v>89.15059395259671</v>
       </c>
       <c r="C21" t="n">
-        <v>4.361301512682162e-15</v>
+        <v>2.41011396868777e-15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>recruit</t>
+          <t>finish</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84.27541908946336</v>
+        <v>83.65361043951613</v>
       </c>
       <c r="C22" t="n">
-        <v>2.276274174059086e-14</v>
+        <v>3.028789286685058e-14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>resident</t>
+          <t>bodies</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>83.11485961387041</v>
+        <v>81.42955351081156</v>
       </c>
       <c r="C23" t="n">
-        <v>3.878643865651044e-14</v>
+        <v>8.400102573431218e-14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hereditary</t>
+          <t>clarke</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>80.51848355361984</v>
+        <v>80.21476619107125</v>
       </c>
       <c r="C24" t="n">
-        <v>1.274839772004147e-13</v>
+        <v>1.464908819847117e-13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>clarke</t>
+          <t>hereditary</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>78.25885601912762</v>
+        <v>79.54135365019306</v>
       </c>
       <c r="C25" t="n">
-        <v>3.580877625740564e-13</v>
+        <v>1.993232130551048e-13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bodies</t>
+          <t>ownership</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>77.36246682789998</v>
+        <v>78.28606850922323</v>
       </c>
       <c r="C26" t="n">
-        <v>5.390056874167312e-13</v>
+        <v>3.53667235210973e-13</v>
       </c>
     </row>
     <row r="27">
@@ -1807,36 +1807,36 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77.26365685329694</v>
+        <v>77.5642173750781</v>
       </c>
       <c r="C27" t="n">
-        <v>5.638441648373173e-13</v>
+        <v>4.916280714127219e-13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prosecutors</t>
+          <t>accountability</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>75.42021733564029</v>
+        <v>72.41716445398266</v>
       </c>
       <c r="C28" t="n">
-        <v>1.305414016859156e-12</v>
+        <v>5.103013915771494e-12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>railway</t>
+          <t>mayor</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>75.29687435165168</v>
+        <v>71.63202848028801</v>
       </c>
       <c r="C29" t="n">
-        <v>1.380741793623838e-12</v>
+        <v>7.28157232114645e-12</v>
       </c>
     </row>
     <row r="30">
@@ -1846,296 +1846,296 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>70.02399434910048</v>
+        <v>70.32523935857432</v>
       </c>
       <c r="C30" t="n">
-        <v>1.506286578672312e-11</v>
+        <v>1.314694359042249e-11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>accountability</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>69.4369007819479</v>
+        <v>69.06501409550766</v>
       </c>
       <c r="C31" t="n">
-        <v>1.963258044662972e-11</v>
+        <v>2.321742980586162e-11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nights</t>
+          <t>pip</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67.37537068011522</v>
+        <v>68.69722739996138</v>
       </c>
       <c r="C32" t="n">
-        <v>4.968391897020527e-11</v>
+        <v>2.740357352210119e-11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>psychologists</t>
+          <t>helpful</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.50637797691696</v>
+        <v>64.90445045525328</v>
       </c>
       <c r="C33" t="n">
-        <v>2.814043894812524e-10</v>
+        <v>1.505798748885874e-10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hosts</t>
+          <t>psychologists</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>60.25341508201461</v>
+        <v>63.49033603157635</v>
       </c>
       <c r="C34" t="n">
-        <v>1.198062715425018e-09</v>
+        <v>2.83428127995859e-10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>lady</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>57.85234830046974</v>
+        <v>61.59703401005784</v>
       </c>
       <c r="C35" t="n">
-        <v>3.469328258446452e-09</v>
+        <v>6.593085296596573e-10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>harlow</t>
+          <t>hosts</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>57.441637340974</v>
+        <v>60.34052046581602</v>
       </c>
       <c r="C36" t="n">
-        <v>4.159052630958721e-09</v>
+        <v>1.152615590375765e-09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>howell</t>
+          <t>josh</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>56.32672452296826</v>
+        <v>58.20720784086576</v>
       </c>
       <c r="C37" t="n">
-        <v>6.798301868702944e-09</v>
+        <v>2.965842371663876e-09</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mccartney</t>
+          <t>howell</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>55.27341820264862</v>
+        <v>57.83868978635864</v>
       </c>
       <c r="C38" t="n">
-        <v>1.080212451867058e-08</v>
+        <v>3.49032123580518e-09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hart</t>
+          <t>harlow</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.05898749781074</v>
+        <v>56.77884257419947</v>
       </c>
       <c r="C39" t="n">
-        <v>1.186830916010596e-08</v>
+        <v>5.570901241438149e-09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>medal</t>
+          <t>mccartney</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>54.85940033245375</v>
+        <v>56.73853876089193</v>
       </c>
       <c r="C40" t="n">
-        <v>1.295446883940828e-08</v>
+        <v>5.670715533768503e-09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ownership</t>
+          <t>medal</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>54.50765771988163</v>
+        <v>56.43639470141797</v>
       </c>
       <c r="C41" t="n">
-        <v>1.511464439419304e-08</v>
+        <v>6.47787383623246e-09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>philip</t>
+          <t>hart</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>54.35553984536303</v>
+        <v>56.2460109562867</v>
       </c>
       <c r="C42" t="n">
-        <v>1.615645153055662e-08</v>
+        <v>7.044152652756939e-09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>marcus</t>
+          <t>andrew</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>54.09307462760521</v>
+        <v>55.93980821984299</v>
       </c>
       <c r="C43" t="n">
-        <v>1.812455407400201e-08</v>
+        <v>8.05995715374678e-09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>josh</t>
+          <t>philip</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53.36024043059852</v>
+        <v>55.88358168885482</v>
       </c>
       <c r="C44" t="n">
-        <v>2.497343701461682e-08</v>
+        <v>8.261729639388969e-09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>helpful</t>
+          <t>marcus</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53.08614934297402</v>
+        <v>55.26309274448403</v>
       </c>
       <c r="C45" t="n">
-        <v>2.814997228276861e-08</v>
+        <v>1.085120925054504e-08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>tracey</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52.75417526919914</v>
+        <v>52.98316738738015</v>
       </c>
       <c r="C46" t="n">
-        <v>3.253936682187611e-08</v>
+        <v>2.944460710997997e-08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>andrew</t>
+          <t>fireworks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>51.72251713815837</v>
+        <v>52.8002145463708</v>
       </c>
       <c r="C47" t="n">
-        <v>5.100596283423615e-08</v>
+        <v>3.189222981905489e-08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tracey</t>
+          <t>give</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>51.71798070558147</v>
+        <v>51.52715892094496</v>
       </c>
       <c r="C48" t="n">
-        <v>5.110673441334889e-08</v>
+        <v>5.552967388231789e-08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>commentary</t>
+          <t>anne</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>50.69717943300487</v>
+        <v>51.05757729001275</v>
       </c>
       <c r="C49" t="n">
-        <v>7.96319837264973e-08</v>
+        <v>6.810034775698712e-08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>anne</t>
+          <t>subscribed</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>49.74444864029019</v>
+        <v>50.65866463882561</v>
       </c>
       <c r="C50" t="n">
-        <v>1.203219267254862e-07</v>
+        <v>8.097366125467865e-08</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fireworks</t>
+          <t>robert</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>49.42229310419727</v>
+        <v>50.0115237165512</v>
       </c>
       <c r="C51" t="n">
-        <v>1.383070708485253e-07</v>
+        <v>1.071876894659349e-07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>robert</t>
+          <t>allan</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>49.12341809661291</v>
+        <v>49.29554823463515</v>
       </c>
       <c r="C52" t="n">
-        <v>1.573690438929857e-07</v>
+        <v>1.460933614644573e-07</v>
       </c>
     </row>
     <row r="53">
@@ -2145,192 +2145,192 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>48.97600000014402</v>
+        <v>48.87070206738276</v>
       </c>
       <c r="C53" t="n">
-        <v>1.677100258758595e-07</v>
+        <v>1.755067675204893e-07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>finish</t>
+          <t>sarah</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>48.83445623022441</v>
+        <v>48.45349870210364</v>
       </c>
       <c r="C54" t="n">
-        <v>1.782729873680478e-07</v>
+        <v>2.100981620959766e-07</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>allan</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>48.16005508167444</v>
+        <v>47.83852696563402</v>
       </c>
       <c r="C55" t="n">
-        <v>2.384037897542642e-07</v>
+        <v>2.737779639834354e-07</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hannah</t>
+          <t>china</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>48.02459845887101</v>
+        <v>47.83198109773481</v>
       </c>
       <c r="C56" t="n">
-        <v>2.527167775569981e-07</v>
+        <v>2.745497786135114e-07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>regulatory</t>
+          <t>docherty</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>47.87200098736883</v>
+        <v>47.39782480333075</v>
       </c>
       <c r="C57" t="n">
-        <v>2.698646220796481e-07</v>
+        <v>3.308664792881342e-07</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>adequacy</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>46.68938420484642</v>
+        <v>46.60266517370274</v>
       </c>
       <c r="C58" t="n">
-        <v>4.483607706979056e-07</v>
+        <v>4.653297300926801e-07</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>docherty</t>
+          <t>chris</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>46.07683814672815</v>
+        <v>45.99286632717966</v>
       </c>
       <c r="C59" t="n">
-        <v>5.827506130425648e-07</v>
+        <v>6.040486482984785e-07</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cadet</t>
+          <t>ban</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>45.89671785804095</v>
+        <v>45.54272051859243</v>
       </c>
       <c r="C60" t="n">
-        <v>6.293844755699424e-07</v>
+        <v>7.320855654382864e-07</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>buses</t>
+          <t>adequacy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>44.58650580444404</v>
+        <v>45.09472370424605</v>
       </c>
       <c r="C61" t="n">
-        <v>1.100183199296217e-06</v>
+        <v>8.861756704352657e-07</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>subscribed</t>
+          <t>oath</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>44.43066439692124</v>
+        <v>44.95764502296817</v>
       </c>
       <c r="C62" t="n">
-        <v>1.175539172743449e-06</v>
+        <v>9.394560155387226e-07</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>hartlepool</t>
+          <t>gary</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>44.41316601605963</v>
+        <v>44.83903284508136</v>
       </c>
       <c r="C63" t="n">
-        <v>1.184313498535434e-06</v>
+        <v>9.881135935610115e-07</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sarah</t>
+          <t>hannah</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>44.19075514034808</v>
+        <v>44.67692191334908</v>
       </c>
       <c r="C64" t="n">
-        <v>1.301658780559619e-06</v>
+        <v>1.058679045611564e-06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>gary</t>
+          <t>astrazeneca</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>44.1234648132109</v>
+        <v>44.60015517862461</v>
       </c>
       <c r="C65" t="n">
-        <v>1.339380841265679e-06</v>
+        <v>1.093815829095976e-06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>lady</t>
+          <t>pakistani</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>44.1122838059635</v>
+        <v>44.55663930717561</v>
       </c>
       <c r="C66" t="n">
-        <v>1.345752880419841e-06</v>
+        <v>1.114244216556699e-06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tribunals</t>
+          <t>rees</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>44.06553775968975</v>
+        <v>44.32871881459953</v>
       </c>
       <c r="C67" t="n">
-        <v>1.372720340021131e-06</v>
+        <v>1.227579448698328e-06</v>
       </c>
     </row>
     <row r="68">
@@ -2340,88 +2340,88 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>44.05627597626422</v>
+        <v>43.51289192805005</v>
       </c>
       <c r="C68" t="n">
-        <v>1.378126617227486e-06</v>
+        <v>1.735138733142374e-06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>rees</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>43.34093838391011</v>
+        <v>43.36261541416191</v>
       </c>
       <c r="C69" t="n">
-        <v>1.8661614613703e-06</v>
+        <v>1.849119191201629e-06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>43.15501943418274</v>
+        <v>43.20089410659736</v>
       </c>
       <c r="C70" t="n">
-        <v>2.01886677805688e-06</v>
+        <v>1.980074661361298e-06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ehcps</t>
+          <t>tribunals</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>43.03191227034247</v>
+        <v>42.90896811231454</v>
       </c>
       <c r="C71" t="n">
-        <v>2.126727778298146e-06</v>
+        <v>2.240139472836946e-06</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>astrazeneca</t>
+          <t>jerusalem</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>42.7701661365262</v>
+        <v>42.78580704164153</v>
       </c>
       <c r="C72" t="n">
-        <v>2.37539054090073e-06</v>
+        <v>2.359754282368153e-06</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>oath</t>
+          <t>hartlepool</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>42.75090531732833</v>
+        <v>41.97618836626126</v>
       </c>
       <c r="C73" t="n">
-        <v>2.394786680859344e-06</v>
+        <v>3.319652478565529e-06</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>chris</t>
+          <t>shortly</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>42.52664322546621</v>
+        <v>41.92695593726471</v>
       </c>
       <c r="C74" t="n">
-        <v>2.632502520842477e-06</v>
+        <v>3.389143748837041e-06</v>
       </c>
     </row>
     <row r="75">
@@ -2431,348 +2431,348 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>42.05016184997869</v>
+        <v>40.81494628006523</v>
       </c>
       <c r="C75" t="n">
-        <v>3.217882884616828e-06</v>
+        <v>5.405113093009674e-06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>pakistani</t>
+          <t>andrea</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>41.99872721654479</v>
+        <v>40.63883924357685</v>
       </c>
       <c r="C76" t="n">
-        <v>3.288311538426357e-06</v>
+        <v>5.818583640298826e-06</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jerusalem</t>
+          <t>parish</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>41.88040710749709</v>
+        <v>40.46886108042047</v>
       </c>
       <c r="C77" t="n">
-        <v>3.456170791766118e-06</v>
+        <v>6.247288010566072e-06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>parish</t>
+          <t>holly</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>41.75300172089442</v>
+        <v>40.40049989899698</v>
       </c>
       <c r="C78" t="n">
-        <v>3.646410510074175e-06</v>
+        <v>6.428382130088084e-06</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>anthony</t>
+          <t>engagement</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>41.37349192280336</v>
+        <v>40.23024029465648</v>
       </c>
       <c r="C79" t="n">
-        <v>4.276682079702953e-06</v>
+        <v>6.902293033689749e-06</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>tobacco</t>
+          <t>smith</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>40.61327603315499</v>
+        <v>40.20747675402697</v>
       </c>
       <c r="C80" t="n">
-        <v>5.881146733999467e-06</v>
+        <v>6.968218329536574e-06</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>cigarettes</t>
+          <t>anthony</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>40.58637962823351</v>
+        <v>40.12464398180442</v>
       </c>
       <c r="C81" t="n">
-        <v>5.94769109971984e-06</v>
+        <v>7.213407902119027e-06</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gedling</t>
+          <t>improvement</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>39.98522548564549</v>
+        <v>39.86002062229143</v>
       </c>
       <c r="C82" t="n">
-        <v>7.645501480121125e-06</v>
+        <v>8.055298561511929e-06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>andrea</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>39.73561345253463</v>
+        <v>39.76372933960591</v>
       </c>
       <c r="C83" t="n">
-        <v>8.483979648064958e-06</v>
+        <v>8.385167377207108e-06</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>steven</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>39.41539106731395</v>
+        <v>39.50321364343351</v>
       </c>
       <c r="C84" t="n">
-        <v>9.693919996091082e-06</v>
+        <v>9.346067993255886e-06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>holly</t>
+          <t>responders</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>39.35630507640946</v>
+        <v>39.33555994465645</v>
       </c>
       <c r="C85" t="n">
-        <v>9.935120543565334e-06</v>
+        <v>1.002120545249691e-05</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>way</t>
+          <t>strengthen</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>39.19136483055895</v>
+        <v>39.05856648688686</v>
       </c>
       <c r="C86" t="n">
-        <v>1.064027796493351e-05</v>
+        <v>1.12437776231198e-05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>asylum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>38.63208914173396</v>
+        <v>38.94845387681642</v>
       </c>
       <c r="C87" t="n">
-        <v>1.34199432678321e-05</v>
+        <v>1.176973742477279e-05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>responders</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>38.52791924266398</v>
+        <v>38.77904955110683</v>
       </c>
       <c r="C88" t="n">
-        <v>1.401180726236886e-05</v>
+        <v>1.262673856199381e-05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>steven</t>
+          <t>cass</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>38.45093561041642</v>
+        <v>38.75943151731121</v>
       </c>
       <c r="C89" t="n">
-        <v>1.446570598680497e-05</v>
+        <v>1.272988383021785e-05</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>afriyie</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>38.37013507322937</v>
+        <v>38.55751848368477</v>
       </c>
       <c r="C90" t="n">
-        <v>1.495773302948262e-05</v>
+        <v>1.384105867698689e-05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>solloway</t>
+          <t>john</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.63757094112113</v>
+        <v>38.50078881399866</v>
       </c>
       <c r="C91" t="n">
-        <v>2.024367330193179e-05</v>
+        <v>1.417014085634486e-05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>essence</t>
+          <t>suzanne</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>37.56755914190956</v>
+        <v>38.40938614456635</v>
       </c>
       <c r="C92" t="n">
-        <v>2.083642713397339e-05</v>
+        <v>1.471668688345036e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>suzanne</t>
+          <t>solloway</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>37.52281468948021</v>
+        <v>38.37252083224449</v>
       </c>
       <c r="C93" t="n">
-        <v>2.122419522362916e-05</v>
+        <v>1.494297109532395e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>afriyie</t>
+          <t>baynes</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>37.49973652792288</v>
+        <v>38.20768794234242</v>
       </c>
       <c r="C94" t="n">
-        <v>2.142697281434642e-05</v>
+        <v>1.599749868370295e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>hour</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>37.43822548682738</v>
+        <v>38.18314902521126</v>
       </c>
       <c r="C95" t="n">
-        <v>2.197683104899067e-05</v>
+        <v>1.616064890431611e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>baynes</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>37.40166146023181</v>
+        <v>38.04141063733834</v>
       </c>
       <c r="C96" t="n">
-        <v>2.231025913735004e-05</v>
+        <v>1.713568070604679e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>carrier</t>
+          <t>fluctuating</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>37.22466423683679</v>
+        <v>38.00849708778116</v>
       </c>
       <c r="C97" t="n">
-        <v>2.399621494513357e-05</v>
+        <v>1.737027925396883e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>mark</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>37.05559633306226</v>
+        <v>37.93308590630143</v>
       </c>
       <c r="C98" t="n">
-        <v>2.572380597129297e-05</v>
+        <v>1.791981322173159e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>vara</t>
+          <t>avanti</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>36.93313591270363</v>
+        <v>37.91033994015409</v>
       </c>
       <c r="C99" t="n">
-        <v>2.705123236062609e-05</v>
+        <v>1.80889114926598e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>shailesh</t>
+          <t>vara</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>36.93313591270363</v>
+        <v>37.74434045755017</v>
       </c>
       <c r="C100" t="n">
-        <v>2.705123236062609e-05</v>
+        <v>1.937161662253069e-05</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>shailesh</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>36.85653453065817</v>
+        <v>37.74434045755017</v>
       </c>
       <c r="C101" t="n">
-        <v>2.791568731124188e-05</v>
+        <v>1.937161662253069e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2804,51 +2804,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>hon</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.213162796322741</v>
+        <v>1.165226468560022</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hon</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.20601496733197</v>
+        <v>1.098563088745621</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>make</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.141303926325442</v>
+        <v>1.073595117464573</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>make</t>
+          <t>government</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.114540756748849</v>
+        <v>1.068311589284839</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>government</t>
+          <t>bill</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.109642130787396</v>
+        <v>1.06571344009393</v>
       </c>
     </row>
     <row r="7">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.099150087336276</v>
+        <v>1.058905047638674</v>
       </c>
     </row>
     <row r="8">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.082386161263733</v>
+        <v>1.046425027154773</v>
       </c>
     </row>
     <row r="9">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.064505853329943</v>
+        <v>1.026768414890154</v>
       </c>
     </row>
     <row r="10">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.059637726030153</v>
+        <v>1.019241687993387</v>
       </c>
     </row>
     <row r="11">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.029851069961971</v>
+        <v>0.9924041972875934</v>
       </c>
     </row>
     <row r="12">
@@ -2908,897 +2908,897 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.014622769361666</v>
+        <v>0.9741853879010971</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>house</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.009920329215174</v>
+        <v>0.9718949742083619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>right</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.009046690114476</v>
+        <v>0.9709070207816567</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>david</t>
+          <t>also</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.996478145966248</v>
+        <v>0.9644471416948774</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>take</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9914769838661144</v>
+        <v>0.9635834291193464</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mark</t>
+          <t>david</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9871175353196342</v>
+        <v>0.9598366871004862</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>mark</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9810977320710517</v>
+        <v>0.9568990862320608</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>would</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9615899273746371</v>
+        <v>0.9552531873427029</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>support</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.961112118698414</v>
+        <v>0.9494958394402579</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9601384840625178</v>
+        <v>0.940667890530844</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>know</t>
+          <t>john</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9507478116489102</v>
+        <v>0.9328884157373939</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>need</t>
+          <t>green</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9457878971236111</v>
+        <v>0.9253285265722091</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>well</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9248319033673267</v>
+        <v>0.9229375831542949</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>come</t>
+          <t>say</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9109726754679096</v>
+        <v>0.9193570260317094</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>know</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9058934001084372</v>
+        <v>0.9093800763746931</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>west</t>
+          <t>many</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8992287654202278</v>
+        <v>0.9074851502487865</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>include</t>
+          <t>need</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8985192163311743</v>
+        <v>0.9047802685970519</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chris</t>
+          <t>go</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8976364374939623</v>
+        <v>0.8990825017659636</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>one</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8970368527311916</v>
+        <v>0.8976436184979233</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>get</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8940123545828894</v>
+        <v>0.8883493273463401</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>james</t>
+          <t>law</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8911336471882876</v>
+        <v>0.8876618284889304</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>give</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8899014310498632</v>
+        <v>0.8759843595440737</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>chris</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.886957031453866</v>
+        <v>0.8736898531325478</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>come</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8812295903396171</v>
+        <v>0.8719906015685506</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>minister</t>
+          <t>west</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8797051564090299</v>
+        <v>0.8624078910606423</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>james</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8770360347715827</v>
+        <v>0.8606246065991724</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>want</t>
+          <t>first</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8691392645041267</v>
+        <v>0.8593757510634656</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>champion</t>
+          <t>include</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8660112754156761</v>
+        <v>0.858844668679649</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>place</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8528522052860394</v>
+        <v>0.8585690072781216</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>look</t>
+          <t>see</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8470283544022794</v>
+        <v>0.8573873562455674</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>country</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.846829577550811</v>
+        <v>0.8547955025375945</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>change</t>
+          <t>good</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8432913426407586</v>
+        <v>0.8526945888409914</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>important</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8430162406395636</v>
+        <v>0.8496709428192648</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>last</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8394121725988064</v>
+        <v>0.8437064989791446</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>paul</t>
+          <t>new</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8375374686163647</v>
+        <v>0.8404868666558272</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ensure</t>
+          <t>day</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8362527519928851</v>
+        <v>0.8391013619178672</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>thank</t>
+          <t>minister</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8341501034615868</v>
+        <v>0.8380812712236625</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pay</t>
+          <t>want</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8309433758171911</v>
+        <v>0.8304101468293236</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hall</t>
+          <t>champion</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8306940809786634</v>
+        <v>0.8294962422266439</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>andrew</t>
+          <t>across</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8301311557115326</v>
+        <v>0.8224724218428774</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>constituency</t>
+          <t>great</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8289528883594779</v>
+        <v>0.8174393424019271</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>paul</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8238965510438172</v>
+        <v>0.8124674973969789</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>richard</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8225814474710877</v>
+        <v>0.8076176083504187</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>help</t>
+          <t>look</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8206878760531053</v>
+        <v>0.8074889926327695</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sarah</t>
+          <t>richard</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8201308771135948</v>
+        <v>0.8068326126367518</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8198978692218939</v>
+        <v>0.8058975128091703</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>way</t>
+          <t>change</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8174333490179082</v>
+        <v>0.804459510123498</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>smith</t>
+          <t>important</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8171848517616407</v>
+        <v>0.8043229567791362</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>issue</t>
+          <t>andrew</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8155231425057163</v>
+        <v>0.8033319246322135</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>smith</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8154566051010481</v>
+        <v>0.7990595065890487</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>far</t>
+          <t>part</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8115035526984039</v>
+        <v>0.7988534901556714</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>peter</t>
+          <t>hall</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.808381337775808</v>
+        <v>0.7985148624244754</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>ensure</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8080822205624512</v>
+        <v>0.7964325210543874</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>debate</t>
+          <t>thank</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7987177504564011</v>
+        <v>0.7951811590233067</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>like</t>
+          <t>two</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7971912574236341</v>
+        <v>0.7934749259712851</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>george</t>
+          <t>pay</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7965819736403851</v>
+        <v>0.792786609091891</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jim</t>
+          <t>sarah</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7953449456681946</v>
+        <v>0.7903657979190328</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jones</t>
+          <t>constituency</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7937652625491405</v>
+        <v>0.7900532184006015</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>local</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7922560821950021</v>
+        <v>0.7846431896497299</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>stephen</t>
+          <t>peter</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7917928354054475</v>
+        <v>0.7841776726725871</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>hope</t>
+          <t>much</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7907323702306869</v>
+        <v>0.7824608941600332</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dr</t>
+          <t>help</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7891911334474697</v>
+        <v>0.7803830540397517</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>point</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7823449895047343</v>
+        <v>0.7802469307739396</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>provide</t>
+          <t>community</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7822365997871108</v>
+        <v>0.7791124023246161</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>bring</t>
+          <t>way</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7814465288205008</v>
+        <v>0.7779567063363357</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>issue</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7801693511165202</v>
+        <v>0.7763378499062691</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>martin</t>
+          <t>jones</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7785933503029456</v>
+        <v>0.7756857754318651</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>stephen</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7781113364910375</v>
+        <v>0.7745840352138265</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>labour</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7780367874410601</v>
+        <v>0.7729351906791211</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>far</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7776146624259568</v>
+        <v>0.7722335450225648</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>life</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7754122890613991</v>
+        <v>0.7714866111358905</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>raise</t>
+          <t>george</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.775184186348042</v>
+        <v>0.7709833871414333</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>secretary</t>
+          <t>may</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7744819526373072</v>
+        <v>0.7622359571818078</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>debate</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7728548431605904</v>
+        <v>0.7616124525445738</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>opportunity</t>
+          <t>like</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7727481161782068</v>
+        <v>0.7587678695183506</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7697255360242422</v>
+        <v>0.7563515820830903</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>western</t>
+          <t>public</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7674985895685731</v>
+        <v>0.7554708690087104</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ben</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7671249517531555</v>
+        <v>0.7549297904241137</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>meet</t>
+          <t>martin</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7666493629190296</v>
+        <v>0.7547854570683838</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>national</t>
+          <t>back</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7665469741915329</v>
+        <v>0.7543395464974832</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>johnson</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7664232588658544</v>
+        <v>0.7520324386385384</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>hope</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7657727727172217</v>
+        <v>0.7519702877047925</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>johnson</t>
+          <t>bring</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7651079570351476</v>
+        <v>0.7447739743253701</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>deliver</t>
+          <t>point</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7639963176667587</v>
+        <v>0.7446156908451931</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>provide</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7624172297152449</v>
+        <v>0.7440673084154644</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>week</t>
+          <t>every</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7591651490458187</v>
+        <v>0.74302587615409</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>ben</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7583636575782511</v>
+        <v>0.742248526592362</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>think</t>
+          <t>tom</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.757450455553234</v>
+        <v>0.7415126457175072</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>labour</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7573770868771752</v>
+        <v>0.7409354081590178</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>steve</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7546335351392924</v>
+        <v>0.7407420344740943</v>
       </c>
     </row>
   </sheetData>
@@ -3835,40 +3835,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>marsh</t>
+          <t>bodies</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>777.949653371785</v>
+        <v>755.08890222277</v>
       </c>
       <c r="C2" t="n">
-        <v>1.184064749132286e-161</v>
+        <v>9.824407012471328e-157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>delegated</t>
+          <t>marsh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>616.2556764238241</v>
+        <v>673.9356409265945</v>
       </c>
       <c r="C3" t="n">
-        <v>6.786396765394992e-127</v>
+        <v>2.768032296805351e-139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bodies</t>
+          <t>delegated</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>346.0555162912131</v>
+        <v>531.7273909538407</v>
       </c>
       <c r="C4" t="n">
-        <v>4.281373358906124e-69</v>
+        <v>9.188822821602551e-109</v>
       </c>
     </row>
     <row r="5">
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>311.2715256602737</v>
+        <v>324.5571478144977</v>
       </c>
       <c r="C5" t="n">
-        <v>1.058763443730804e-61</v>
+        <v>1.59584410885817e-64</v>
       </c>
     </row>
     <row r="6">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>295.1804887563838</v>
+        <v>312.2463649620751</v>
       </c>
       <c r="C6" t="n">
-        <v>2.746500606277918e-58</v>
+        <v>6.574117784383455e-62</v>
       </c>
     </row>
     <row r="7">
@@ -3904,23 +3904,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>263.6061330520091</v>
+        <v>278.9861782508817</v>
       </c>
       <c r="C7" t="n">
-        <v>1.331521404503182e-51</v>
+        <v>7.415939551143311e-55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ukrainian</t>
+          <t>dogs</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>232.4845778374138</v>
+        <v>215.4935866198253</v>
       </c>
       <c r="C8" t="n">
-        <v>4.930665101592549e-45</v>
+        <v>1.854119412552733e-41</v>
       </c>
     </row>
     <row r="9">
@@ -3930,23 +3930,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>204.4146785408605</v>
+        <v>212.9704651110693</v>
       </c>
       <c r="C9" t="n">
-        <v>3.930424036518004e-39</v>
+        <v>6.284831141977601e-41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dogs</t>
+          <t>ukrainian</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>192.6395247715066</v>
+        <v>204.8956862359921</v>
       </c>
       <c r="C10" t="n">
-        <v>1.153773936256168e-36</v>
+        <v>3.115495129208839e-39</v>
       </c>
     </row>
     <row r="11">
@@ -3956,179 +3956,179 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>157.2036613292736</v>
+        <v>164.6582936401618</v>
       </c>
       <c r="C11" t="n">
-        <v>2.828451020945283e-29</v>
+        <v>7.985970606934262e-31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>repair</t>
+          <t>livestock</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>138.9883569870908</v>
+        <v>130.2251079836763</v>
       </c>
       <c r="C12" t="n">
-        <v>1.668558856995249e-25</v>
+        <v>1.066025832671326e-23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lock</t>
+          <t>stourbridge</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>129.9143825238474</v>
+        <v>130.0311162491517</v>
       </c>
       <c r="C13" t="n">
-        <v>1.234999453636828e-23</v>
+        <v>1.168589773752752e-23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stourbridge</t>
+          <t>craig</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>124.0369417824161</v>
+        <v>125.2218172946112</v>
       </c>
       <c r="C14" t="n">
-        <v>1.989295972266634e-22</v>
+        <v>1.136634845301299e-22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>livestock</t>
+          <t>fletcher</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>115.878931018795</v>
+        <v>122.9404833195346</v>
       </c>
       <c r="C15" t="n">
-        <v>9.301291019139413e-21</v>
+        <v>3.33825569931697e-22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>brecon</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>103.3526508479154</v>
+        <v>122.5159206957493</v>
       </c>
       <c r="C16" t="n">
-        <v>3.295825792884798e-18</v>
+        <v>4.078885961166131e-22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>speakers</t>
+          <t>lock</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99.5009561919496</v>
+        <v>114.9569586121603</v>
       </c>
       <c r="C17" t="n">
-        <v>1.985134189282774e-17</v>
+        <v>1.434896042785987e-20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mayor</t>
+          <t>clarke</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>95.77820110814889</v>
+        <v>110.4141957517243</v>
       </c>
       <c r="C18" t="n">
-        <v>1.120563403114979e-16</v>
+        <v>1.210873133533426e-19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>clare</t>
+          <t>brecon</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>95.72074388722081</v>
+        <v>108.4116517266014</v>
       </c>
       <c r="C19" t="n">
-        <v>1.150854972953743e-16</v>
+        <v>3.09489740881692e-19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>leamington</t>
+          <t>speakers</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>95.49155395315273</v>
+        <v>104.9696351702993</v>
       </c>
       <c r="C20" t="n">
-        <v>1.28003904271316e-16</v>
+        <v>1.548717221342712e-18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>penkridge</t>
+          <t>clare</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94.23418265967889</v>
+        <v>102.0656218967247</v>
       </c>
       <c r="C21" t="n">
-        <v>2.29375943604427e-16</v>
+        <v>6.008594550368122e-18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>craig</t>
+          <t>leamington</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93.17458827469666</v>
+        <v>100.32858976674</v>
       </c>
       <c r="C22" t="n">
-        <v>3.748224063308793e-16</v>
+        <v>1.350216146098036e-17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>wyrley</t>
+          <t>penkridge</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>92.94017590432408</v>
+        <v>99.17118151051767</v>
       </c>
       <c r="C23" t="n">
-        <v>4.178144014503673e-16</v>
+        <v>2.314503775420478e-17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fletcher</t>
+          <t>wyrley</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92.75416733423188</v>
+        <v>97.80320948147468</v>
       </c>
       <c r="C24" t="n">
-        <v>4.554042431991852e-16</v>
+        <v>4.373581497473783e-17</v>
       </c>
     </row>
     <row r="25">
@@ -4138,36 +4138,36 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>86.82226437826884</v>
+        <v>91.51269293229316</v>
       </c>
       <c r="C25" t="n">
-        <v>7.052550859530478e-15</v>
+        <v>8.090138926698548e-16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>eighty</t>
+          <t>midwifery</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>86.30357079948338</v>
+        <v>88.95804502375702</v>
       </c>
       <c r="C26" t="n">
-        <v>8.955468471753974e-15</v>
+        <v>2.63413905431738e-15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>biggin</t>
+          <t>businesses</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>86.12766976988389</v>
+        <v>88.51620308079769</v>
       </c>
       <c r="C27" t="n">
-        <v>9.710862981792628e-15</v>
+        <v>3.229914051588195e-15</v>
       </c>
     </row>
     <row r="28">
@@ -4177,75 +4177,75 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>85.86331851195744</v>
+        <v>88.44491311575354</v>
       </c>
       <c r="C28" t="n">
-        <v>1.09673237477603e-14</v>
+        <v>3.337914869022134e-15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>clarke</t>
+          <t>tamar</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>82.27441029016244</v>
+        <v>86.46020563123152</v>
       </c>
       <c r="C29" t="n">
-        <v>5.703206043282171e-14</v>
+        <v>8.332317376567516e-15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>skye</t>
+          <t>federation</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>80.09899051543952</v>
+        <v>85.69836463665446</v>
       </c>
       <c r="C30" t="n">
-        <v>1.544586425393499e-13</v>
+        <v>1.183225155493596e-14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>littlehampton</t>
+          <t>skye</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>79.60862798629842</v>
+        <v>84.90421058947872</v>
       </c>
       <c r="C31" t="n">
-        <v>1.932862911481749e-13</v>
+        <v>1.70493223414971e-14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>businesses</t>
+          <t>length</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>78.54465833730859</v>
+        <v>84.9039576588906</v>
       </c>
       <c r="C32" t="n">
-        <v>3.142844308137981e-13</v>
+        <v>1.705130516721449e-14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>midwifery</t>
+          <t>littlehampton</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>78.2797352025737</v>
+        <v>83.90214609287995</v>
       </c>
       <c r="C33" t="n">
-        <v>3.546911633726346e-13</v>
+        <v>2.7020802027269e-14</v>
       </c>
     </row>
     <row r="34">
@@ -4255,23 +4255,23 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>77.17498637517932</v>
+        <v>81.47092377854005</v>
       </c>
       <c r="C34" t="n">
-        <v>5.871040435462042e-13</v>
+        <v>8.242398025375269e-14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>federation</t>
+          <t>mccartney</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>75.85232600877228</v>
+        <v>80.9885200160624</v>
       </c>
       <c r="C35" t="n">
-        <v>1.072414659951843e-12</v>
+        <v>1.028038025673549e-13</v>
       </c>
     </row>
     <row r="36">
@@ -4281,452 +4281,452 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>74.33093618544798</v>
+        <v>79.55419949358732</v>
       </c>
       <c r="C36" t="n">
-        <v>2.141816009726264e-12</v>
+        <v>1.981561294691256e-13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>howell</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>74.22596941419886</v>
+        <v>79.49467408710545</v>
       </c>
       <c r="C37" t="n">
-        <v>2.246401696875587e-12</v>
+        <v>2.036222159992957e-13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tamar</t>
+          <t>hart</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>74.13221568810863</v>
+        <v>78.55837517001031</v>
       </c>
       <c r="C38" t="n">
-        <v>2.344112332499747e-12</v>
+        <v>3.123221046669154e-13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>beckton</t>
+          <t>philip</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>71.69167037810875</v>
+        <v>77.09289381584831</v>
       </c>
       <c r="C39" t="n">
-        <v>7.087653288283045e-12</v>
+        <v>6.094905707135588e-13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>broughty</t>
+          <t>substation</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>70.93472892491233</v>
+        <v>76.79179462698049</v>
       </c>
       <c r="C40" t="n">
-        <v>9.981744153131135e-12</v>
+        <v>6.991362630370148e-13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bognor</t>
+          <t>broughty</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>68.72869030592722</v>
+        <v>76.38618368022649</v>
       </c>
       <c r="C41" t="n">
-        <v>2.701780299807807e-11</v>
+        <v>8.410215697361852e-13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>substation</t>
+          <t>beckton</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68.22698553588108</v>
+        <v>76.35717524222159</v>
       </c>
       <c r="C42" t="n">
-        <v>3.386849698552765e-11</v>
+        <v>8.522059507846054e-13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>didcot</t>
+          <t>eighty</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66.99503430866854</v>
+        <v>76.31320144806334</v>
       </c>
       <c r="C43" t="n">
-        <v>5.894769328286019e-11</v>
+        <v>8.694438009098757e-13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>shotts</t>
+          <t>marcus</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66.50869739270517</v>
+        <v>75.2602071984425</v>
       </c>
       <c r="C44" t="n">
-        <v>7.33406524697438e-11</v>
+        <v>1.40395978729265e-12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>wythenshawe</t>
+          <t>bognor</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65.63941062768619</v>
+        <v>72.60894916207866</v>
       </c>
       <c r="C45" t="n">
-        <v>1.083280597267866e-10</v>
+        <v>4.678280295985e-12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>wantage</t>
+          <t>banking</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65.27730944588572</v>
+        <v>71.548557208183</v>
       </c>
       <c r="C46" t="n">
-        <v>1.274176844171399e-10</v>
+        <v>7.561882124161133e-12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bathgate</t>
+          <t>arm</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64.70868038099917</v>
+        <v>71.10327145982534</v>
       </c>
       <c r="C47" t="n">
-        <v>1.643743150277837e-10</v>
+        <v>9.249315471712311e-12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dominic</t>
+          <t>shotts</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>62.95870675662544</v>
+        <v>70.83632973937775</v>
       </c>
       <c r="C48" t="n">
-        <v>3.593566388550878e-10</v>
+        <v>1.043579256608641e-11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>barr</t>
+          <t>didcot</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>62.0932366820327</v>
+        <v>70.80752309455643</v>
       </c>
       <c r="C49" t="n">
-        <v>5.285950696456151e-10</v>
+        <v>1.057257100340399e-11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>loudoun</t>
+          <t>anne</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>61.43416871525546</v>
+        <v>70.06562604616175</v>
       </c>
       <c r="C50" t="n">
-        <v>7.088704878545526e-10</v>
+        <v>1.47823677644879e-11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>banking</t>
+          <t>wythenshawe</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>61.08663278134248</v>
+        <v>69.5341107637326</v>
       </c>
       <c r="C51" t="n">
-        <v>8.273789708101459e-10</v>
+        <v>1.879019667765302e-11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>elizabeth</t>
+          <t>services</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>61.02936568458314</v>
+        <v>69.51903517588489</v>
       </c>
       <c r="C52" t="n">
-        <v>8.487173008098407e-10</v>
+        <v>1.891843571191897e-11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>tracey</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>60.56184967387773</v>
+        <v>69.257767438209</v>
       </c>
       <c r="C53" t="n">
-        <v>1.044710804017253e-09</v>
+        <v>2.128467932391381e-11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>coatbridge</t>
+          <t>wantage</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>60.27899986833823</v>
+        <v>68.88114902382316</v>
       </c>
       <c r="C54" t="n">
-        <v>1.184531939396891e-09</v>
+        <v>2.522378286041113e-11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>mccartney</t>
+          <t>bathgate</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>60.01433416548853</v>
+        <v>68.49526714047072</v>
       </c>
       <c r="C55" t="n">
-        <v>1.332178143461242e-09</v>
+        <v>3.001393304196403e-11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>yarmouth</t>
+          <t>allan</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>59.9241254329971</v>
+        <v>68.40111890070692</v>
       </c>
       <c r="C56" t="n">
-        <v>1.386577627525547e-09</v>
+        <v>3.131409023238252e-11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tata</t>
+          <t>subscribe</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>59.8370381077313</v>
+        <v>68.16480207594802</v>
       </c>
       <c r="C57" t="n">
-        <v>1.441191159319554e-09</v>
+        <v>3.483013868902515e-11</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>howell</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>59.35864148000925</v>
+        <v>67.21447681482391</v>
       </c>
       <c r="C58" t="n">
-        <v>1.781686560937011e-09</v>
+        <v>5.34111382676269e-11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>robert</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>58.753141864565</v>
+        <v>66.63719448862666</v>
       </c>
       <c r="C59" t="n">
-        <v>2.329601669865802e-09</v>
+        <v>6.922835675895412e-11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>philip</t>
+          <t>dominic</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>58.52367147052898</v>
+        <v>66.39981741559228</v>
       </c>
       <c r="C60" t="n">
-        <v>2.578545013640036e-09</v>
+        <v>7.701502115792113e-11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hart</t>
+          <t>barr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>58.12925438020351</v>
+        <v>66.0470156790504</v>
       </c>
       <c r="C61" t="n">
-        <v>3.069812104587615e-09</v>
+        <v>9.022822929296718e-11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>andrew</t>
+          <t>release</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>57.70947520795514</v>
+        <v>65.95207286464739</v>
       </c>
       <c r="C62" t="n">
-        <v>3.695283254173899e-09</v>
+        <v>9.415458516551726e-11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>heywood</t>
+          <t>elizabeth</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>57.26412066319978</v>
+        <v>64.68452997679803</v>
       </c>
       <c r="C63" t="n">
-        <v>4.497891360661165e-09</v>
+        <v>1.6616098019567e-10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>arap</t>
+          <t>mayor</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>57.09243098473458</v>
+        <v>64.38863981809529</v>
       </c>
       <c r="C64" t="n">
-        <v>4.851702037413275e-09</v>
+        <v>1.896867747456917e-10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>caseworker</t>
+          <t>accountability</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>56.81636087473559</v>
+        <v>64.20627899771955</v>
       </c>
       <c r="C65" t="n">
-        <v>5.479556978018949e-09</v>
+        <v>2.058093232669135e-10</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>exploitation</t>
+          <t>caseworker</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>56.63264166239432</v>
+        <v>63.66322377441064</v>
       </c>
       <c r="C66" t="n">
-        <v>5.94153409143525e-09</v>
+        <v>2.623605756131378e-10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>preseli</t>
+          <t>yarmouth</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>56.54951729228879</v>
+        <v>63.60328099443522</v>
       </c>
       <c r="C67" t="n">
-        <v>6.163095518507279e-09</v>
+        <v>2.694822104677804e-10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>marcus</t>
+          <t>prepayment</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>56.38834952658223</v>
+        <v>63.59247497439664</v>
       </c>
       <c r="C68" t="n">
-        <v>6.616357268122087e-09</v>
+        <v>2.707863750605478e-10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>redesign</t>
+          <t>docherty</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>55.83682191314381</v>
+        <v>63.45192870212957</v>
       </c>
       <c r="C69" t="n">
-        <v>8.433350770653832e-09</v>
+        <v>2.88332413286678e-10</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>prepayment</t>
+          <t>exploitation</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>55.30201147538796</v>
+        <v>63.05341024022148</v>
       </c>
       <c r="C70" t="n">
-        <v>1.066734840097582e-08</v>
+        <v>3.444847900050478e-10</v>
       </c>
     </row>
     <row r="71">
@@ -4736,400 +4736,400 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>55.26622822263595</v>
+        <v>62.17229127119433</v>
       </c>
       <c r="C71" t="n">
-        <v>1.083628053973206e-08</v>
+        <v>5.102999986743335e-10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>shire</t>
+          <t>andrew</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>55.15159009586193</v>
+        <v>62.03196801436918</v>
       </c>
       <c r="C72" t="n">
-        <v>1.139560612779166e-08</v>
+        <v>5.432220466808609e-10</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>inverness</t>
+          <t>heywood</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>54.66677410870929</v>
+        <v>61.95611985573431</v>
       </c>
       <c r="C73" t="n">
-        <v>1.409634106633916e-08</v>
+        <v>5.61889087689124e-10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>renfrewshire</t>
+          <t>rees</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>54.42052800508819</v>
+        <v>61.59779535982182</v>
       </c>
       <c r="C74" t="n">
-        <v>1.570290727384151e-08</v>
+        <v>6.590851389878888e-10</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dale</t>
+          <t>preseli</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>54.20214604448775</v>
+        <v>60.43130623358586</v>
       </c>
       <c r="C75" t="n">
-        <v>1.727928377159849e-08</v>
+        <v>1.107074041323443e-09</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>fleetwood</t>
+          <t>coatbridge</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>53.83003705825179</v>
+        <v>59.16549450862112</v>
       </c>
       <c r="C76" t="n">
-        <v>2.033595116005151e-08</v>
+        <v>1.94085739491272e-09</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>coke</t>
+          <t>shire</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>53.75486570775407</v>
+        <v>58.92310520919795</v>
       </c>
       <c r="C77" t="n">
-        <v>2.101583483455454e-08</v>
+        <v>2.160772843857645e-09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>penrith</t>
+          <t>renfrewshire</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>53.55897376266223</v>
+        <v>58.89007180211942</v>
       </c>
       <c r="C78" t="n">
-        <v>2.289560933773404e-08</v>
+        <v>2.192603700955726e-09</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>furnace</t>
+          <t>gary</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>53.52843450009727</v>
+        <v>58.37935946918871</v>
       </c>
       <c r="C79" t="n">
-        <v>2.32033566724855e-08</v>
+        <v>2.748485058498109e-09</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>josh</t>
+          <t>pier</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>53.12895753875867</v>
+        <v>58.08564988967744</v>
       </c>
       <c r="C80" t="n">
-        <v>2.762860685770423e-08</v>
+        <v>3.12954273628283e-09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>inverness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>53.09738531506574</v>
+        <v>58.04938615427159</v>
       </c>
       <c r="C81" t="n">
-        <v>2.801218910653832e-08</v>
+        <v>3.180097603626118e-09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>funded</t>
+          <t>fleetwood</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>52.82242234179788</v>
+        <v>57.49084071466563</v>
       </c>
       <c r="C82" t="n">
-        <v>3.158466240164628e-08</v>
+        <v>4.069715189990576e-09</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>anne</t>
+          <t>holly</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>52.705099697654</v>
+        <v>57.46145292094832</v>
       </c>
       <c r="C83" t="n">
-        <v>3.324355823704085e-08</v>
+        <v>4.122841640822253e-09</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>penistone</t>
+          <t>funded</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>52.62886181219167</v>
+        <v>57.26723453531693</v>
       </c>
       <c r="C84" t="n">
-        <v>3.436766138121581e-08</v>
+        <v>4.491717339768776e-09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>arbroath</t>
+          <t>tata</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>52.30023848179765</v>
+        <v>57.00370094094056</v>
       </c>
       <c r="C85" t="n">
-        <v>3.966163795375546e-08</v>
+        <v>5.045269267581905e-09</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tracey</t>
+          <t>penrith</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>52.0622008724174</v>
+        <v>56.84680416610346</v>
       </c>
       <c r="C86" t="n">
-        <v>4.399524064863838e-08</v>
+        <v>5.406534199086823e-09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>stocksbridge</t>
+          <t>arbroath</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>51.8526485421658</v>
+        <v>56.38444750259549</v>
       </c>
       <c r="C87" t="n">
-        <v>4.81978225919318e-08</v>
+        <v>6.627732758748443e-09</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>whitehaven</t>
+          <t>andrea</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>51.35717541302368</v>
+        <v>55.88029084806727</v>
       </c>
       <c r="C88" t="n">
-        <v>5.978876712518622e-08</v>
+        <v>8.273693447966101e-09</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>allan</t>
+          <t>penistone</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>51.31781386580948</v>
+        <v>55.67364845495141</v>
       </c>
       <c r="C89" t="n">
-        <v>6.082039756260042e-08</v>
+        <v>9.060493131480826e-09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>bedworth</t>
+          <t>dale</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>51.17580671975257</v>
+        <v>55.56695703304081</v>
       </c>
       <c r="C90" t="n">
-        <v>6.469144916569233e-08</v>
+        <v>9.495414577682591e-09</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>sittingbourne</t>
+          <t>anthony</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>50.46259796495977</v>
+        <v>55.21491742306783</v>
       </c>
       <c r="C91" t="n">
-        <v>8.815978671273379e-08</v>
+        <v>1.108317094201811e-08</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>pinner</t>
+          <t>stocksbridge</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>50.28306175063865</v>
+        <v>54.89702567953557</v>
       </c>
       <c r="C92" t="n">
-        <v>9.529400394479231e-08</v>
+        <v>1.274241143194823e-08</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>pier</t>
+          <t>steven</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>50.13159301842744</v>
+        <v>54.84859047936843</v>
       </c>
       <c r="C93" t="n">
-        <v>1.017568273790955e-07</v>
+        <v>1.301603982860038e-08</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tribunals</t>
+          <t>whitehaven</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>50.10029860682859</v>
+        <v>54.79195999197808</v>
       </c>
       <c r="C94" t="n">
-        <v>1.031453955599695e-07</v>
+        <v>1.334338411378427e-08</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>subscribe</t>
+          <t>bedworth</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>49.83481966854732</v>
+        <v>54.5216272246254</v>
       </c>
       <c r="C95" t="n">
-        <v>1.157078835089914e-07</v>
+        <v>1.502238845658499e-08</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>robert</t>
+          <t>afriyie</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>49.79732850697187</v>
+        <v>53.99902781412163</v>
       </c>
       <c r="C96" t="n">
-        <v>1.176003339986219e-07</v>
+        <v>1.888631371931019e-08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tunbridge</t>
+          <t>tribunals</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>49.67713694173985</v>
+        <v>53.70378288712044</v>
       </c>
       <c r="C97" t="n">
-        <v>1.23876948326255e-07</v>
+        <v>2.149069944547852e-08</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>firework</t>
+          <t>sittingbourne</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>49.42374290607007</v>
+        <v>53.45712078592922</v>
       </c>
       <c r="C98" t="n">
-        <v>1.382204325633606e-07</v>
+        <v>2.393809896124709e-08</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bexleyheath</t>
+          <t>pinner</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>49.05815163813589</v>
+        <v>53.44041929962879</v>
       </c>
       <c r="C99" t="n">
-        <v>1.618668040564497e-07</v>
+        <v>2.411348939139389e-08</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ashfield</t>
+          <t>tunbridge</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>49.02638369235615</v>
+        <v>52.87978670500151</v>
       </c>
       <c r="C100" t="n">
-        <v>1.64102007286224e-07</v>
+        <v>3.080376894683259e-08</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>stirling</t>
+          <t>bexleyheath</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>48.68756455448179</v>
+        <v>52.5839416903215</v>
       </c>
       <c r="C101" t="n">
-        <v>1.899336850888303e-07</v>
+        <v>3.504759826581259e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5143,7 +5143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5182,6 +5182,11 @@
           <t>use_bm25</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>num_stopwords</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5196,17 +5201,20 @@
         <v>10000</v>
       </c>
       <c r="D2" t="n">
-        <v>81.12117336152221</v>
+        <v>80.64853065539113</v>
       </c>
       <c r="E2" t="n">
-        <v>1785937</v>
+        <v>1830649</v>
       </c>
       <c r="F2" t="n">
-        <v>63.27141544895787</v>
+        <v>64.44371763646245</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
+      <c r="H2" t="n">
+        <v>179</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5221,16 +5229,19 @@
         <v>10000</v>
       </c>
       <c r="D3" t="n">
-        <v>83.76429175475687</v>
+        <v>83.262177589852</v>
       </c>
       <c r="E3" t="n">
-        <v>1535898</v>
+        <v>1583398</v>
       </c>
       <c r="F3" t="n">
-        <v>58.93988519615672</v>
+        <v>60.22813701346712</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
